--- a/data/trans_orig/IP3102-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3102-Edad-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14769</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22283</t>
+          <t>21629</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>14634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26504</t>
+          <t>26396</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31699</t>
+          <t>31362</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36415</t>
+          <t>36420</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54331</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>11399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>22617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>14312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>26774</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>28779</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44551</t>
+          <t>45589</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17401</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29594</t>
+          <t>29793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28531</t>
+          <t>28763</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37404</t>
+          <t>37959</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56912</t>
+          <t>55656</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>7801</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19687</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29665</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27536</t>
+          <t>28115</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45362</t>
+          <t>46203</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37637</t>
+          <t>37918</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56791</t>
+          <t>57712</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69944</t>
+          <t>70659</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>97033</t>
+          <t>98108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88365</t>
+          <t>85376</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112001</t>
+          <t>111172</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>92374</t>
+          <t>92916</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116334</t>
+          <t>117895</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>186563</t>
+          <t>186130</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>220736</t>
+          <t>220791</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55760</t>
+          <t>55193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78027</t>
+          <t>77923</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50203</t>
+          <t>51085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72673</t>
+          <t>72856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111584</t>
+          <t>111709</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>142090</t>
+          <t>143362</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28921</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46178</t>
+          <t>47048</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22651</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39542</t>
+          <t>39912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>56447</t>
+          <t>56493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80954</t>
+          <t>81248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>9007</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19770</t>
+          <t>20071</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20475</t>
+          <t>20479</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19989</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t>36406</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22242</t>
+          <t>22523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37233</t>
+          <t>38592</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30449</t>
+          <t>30366</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46550</t>
+          <t>47252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57510</t>
+          <t>56224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79212</t>
+          <t>79393</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>43788</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>60739</t>
+          <t>60811</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39424</t>
+          <t>39754</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57426</t>
+          <t>57765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>87997</t>
+          <t>86115</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>112931</t>
+          <t>112789</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,73%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23903</t>
+          <t>23104</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19198</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34361</t>
+          <t>33465</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33464</t>
+          <t>33725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53174</t>
+          <t>53050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8332</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19685</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>8176</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18742</t>
+          <t>19418</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>34245</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21985</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28093</t>
+          <t>28839</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27964</t>
+          <t>28364</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>48418</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30852</t>
+          <t>30875</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>49629</t>
+          <t>48295</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42329</t>
+          <t>42415</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>61107</t>
+          <t>62076</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>77496</t>
+          <t>77900</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103942</t>
+          <t>105633</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>64335</t>
+          <t>63494</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>87360</t>
+          <t>85258</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65364</t>
+          <t>64787</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86907</t>
+          <t>86930</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>135527</t>
+          <t>134774</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>167834</t>
+          <t>167313</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>59051</t>
+          <t>60514</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48399</t>
+          <t>49614</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>75004</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>103101</t>
+          <t>101374</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9026</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>12088</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24605</t>
+          <t>24339</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>24607</t>
+          <t>24187</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41420</t>
+          <t>40824</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>32154</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53628</t>
+          <t>53690</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34452</t>
+          <t>34307</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>54506</t>
+          <t>55074</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>72091</t>
+          <t>71105</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100559</t>
+          <t>99930</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>97230</t>
+          <t>96656</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128096</t>
+          <t>127570</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129354</t>
+          <t>129458</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>163352</t>
+          <t>163789</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>235004</t>
+          <t>234811</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>281372</t>
+          <t>280244</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>225609</t>
+          <t>227257</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>266540</t>
+          <t>266659</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>233366</t>
+          <t>233365</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>273953</t>
+          <t>274022</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>470996</t>
+          <t>472320</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>528303</t>
+          <t>527924</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>131988</t>
+          <t>132657</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>166601</t>
+          <t>167528</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>129523</t>
+          <t>129273</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>164030</t>
+          <t>162575</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>271462</t>
+          <t>271538</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>318194</t>
+          <t>322382</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>74750</t>
+          <t>76187</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>101520</t>
+          <t>103828</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>70177</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>98495</t>
+          <t>98029</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>152838</t>
+          <t>151291</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>192403</t>
+          <t>190490</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15459</t>
+          <t>15257</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10687</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>15713</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28752</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13216</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24864</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32143</t>
+          <t>30831</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>50193</t>
+          <t>49030</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,2%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12335</t>
+          <t>12215</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11696</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26073</t>
+          <t>26149</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43248</t>
+          <t>42280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35421</t>
+          <t>35664</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50924</t>
+          <t>50998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38065</t>
+          <t>38430</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>53276</t>
+          <t>54039</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78473</t>
+          <t>78475</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99987</t>
+          <t>100538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>15783</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32657</t>
+          <t>33539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52451</t>
+          <t>52247</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>35097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55979</t>
+          <t>55572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74422</t>
+          <t>72981</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102755</t>
+          <t>101267</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68176</t>
+          <t>67366</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92198</t>
+          <t>91121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>72120</t>
+          <t>72389</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>96904</t>
+          <t>97198</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>147424</t>
+          <t>145238</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>180466</t>
+          <t>180148</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31069</t>
+          <t>31054</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50507</t>
+          <t>50141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46152</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67881</t>
+          <t>69392</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81632</t>
+          <t>82231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113094</t>
+          <t>113620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58945</t>
+          <t>58502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81714</t>
+          <t>82765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>64860</t>
+          <t>63349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91456</t>
+          <t>87284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>129385</t>
+          <t>129489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>162901</t>
+          <t>164153</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>10865</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>13977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9920</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21796</t>
+          <t>21706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28189</t>
+          <t>27329</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44725</t>
+          <t>45540</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39806</t>
+          <t>39599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58546</t>
+          <t>58778</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71459</t>
+          <t>71893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98157</t>
+          <t>97352</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>38997</t>
+          <t>39474</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58944</t>
+          <t>58316</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33515</t>
+          <t>33468</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50950</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>78316</t>
+          <t>77573</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>105727</t>
+          <t>104064</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18836</t>
+          <t>19086</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13425</t>
+          <t>13259</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27571</t>
+          <t>27173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36580</t>
+          <t>35649</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57501</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48449</t>
+          <t>49187</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28732</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47403</t>
+          <t>47136</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64651</t>
+          <t>64139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>89803</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8876</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21054</t>
+          <t>20857</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16886</t>
+          <t>17309</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32540</t>
+          <t>32535</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>28562</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>47077</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>42570</t>
+          <t>42998</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>62358</t>
+          <t>62433</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>76649</t>
+          <t>75968</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102541</t>
+          <t>102741</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46626</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67504</t>
+          <t>67212</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57095</t>
+          <t>58650</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>78904</t>
+          <t>79235</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>111541</t>
+          <t>110086</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>139625</t>
+          <t>139540</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,44%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>20071</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36253</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32353</t>
+          <t>32123</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40800</t>
+          <t>41316</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62567</t>
+          <t>61702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26062</t>
+          <t>25843</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>44271</t>
+          <t>44044</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14940</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>29325</t>
+          <t>29836</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45395</t>
+          <t>44942</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>68921</t>
+          <t>67434</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17193</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>32998</t>
+          <t>32681</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>19421</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35587</t>
+          <t>35984</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>38952</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61130</t>
+          <t>62537</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>108490</t>
+          <t>108234</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>142320</t>
+          <t>142094</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>133805</t>
+          <t>133394</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>169348</t>
+          <t>168715</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>251082</t>
+          <t>252045</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>299324</t>
+          <t>301011</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>188382</t>
+          <t>187137</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>227391</t>
+          <t>226750</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>191838</t>
+          <t>194622</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>231284</t>
+          <t>234076</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>391897</t>
+          <t>393009</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>449479</t>
+          <t>449533</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>95442</t>
+          <t>96802</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>127675</t>
+          <t>126998</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>99373</t>
+          <t>100158</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>131266</t>
+          <t>132303</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>203881</t>
+          <t>206858</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>250253</t>
+          <t>252061</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>169007</t>
+          <t>167508</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>206797</t>
+          <t>205638</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>162598</t>
+          <t>161637</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>199227</t>
+          <t>200645</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>342288</t>
+          <t>341140</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>395051</t>
+          <t>394364</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5244</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14452</t>
+          <t>15228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>8703</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19527</t>
+          <t>19980</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26237</t>
+          <t>26369</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25376</t>
+          <t>25677</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41685</t>
+          <t>42026</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>9910</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>18606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32573</t>
+          <t>32332</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43755</t>
+          <t>44131</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58166</t>
+          <t>57786</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37744</t>
+          <t>37473</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51637</t>
+          <t>51816</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86042</t>
+          <t>86114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105530</t>
+          <t>106045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,43%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14916</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10035</t>
+          <t>9545</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21315</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25180</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43210</t>
+          <t>42908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>56109</t>
+          <t>55546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80350</t>
+          <t>81313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43794</t>
+          <t>43476</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64020</t>
+          <t>64025</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52369</t>
+          <t>52943</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75487</t>
+          <t>75995</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>102869</t>
+          <t>101596</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131550</t>
+          <t>131324</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47414</t>
+          <t>47036</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67139</t>
+          <t>67038</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60239</t>
+          <t>60022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>84744</t>
+          <t>83695</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113389</t>
+          <t>111891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>145195</t>
+          <t>143981</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50421</t>
+          <t>50152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69939</t>
+          <t>70655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67671</t>
+          <t>66524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91389</t>
+          <t>90749</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>122944</t>
+          <t>123704</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>154961</t>
+          <t>156139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4510</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8716</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20552</t>
+          <t>20502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30619</t>
+          <t>30690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>28951</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46956</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22720</t>
+          <t>22609</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39260</t>
+          <t>38790</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54821</t>
+          <t>55708</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81675</t>
+          <t>79084</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37858</t>
+          <t>37355</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57274</t>
+          <t>56859</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39030</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58646</t>
+          <t>59228</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>82303</t>
+          <t>82231</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>109820</t>
+          <t>109545</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30980</t>
+          <t>32331</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49378</t>
+          <t>50280</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31192</t>
+          <t>31278</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49666</t>
+          <t>49705</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67652</t>
+          <t>67013</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>93550</t>
+          <t>93127</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43948</t>
+          <t>43157</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>63932</t>
+          <t>64154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46533</t>
+          <t>47028</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>68207</t>
+          <t>67753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92810</t>
+          <t>94711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122995</t>
+          <t>124439</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18768</t>
+          <t>18581</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>23734</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21500</t>
+          <t>21148</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39405</t>
+          <t>38503</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26504</t>
+          <t>27040</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44391</t>
+          <t>45139</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>23925</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40998</t>
+          <t>40982</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54894</t>
+          <t>55435</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79603</t>
+          <t>79755</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>40396</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60206</t>
+          <t>60087</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31341</t>
+          <t>30638</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50588</t>
+          <t>49055</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>74874</t>
+          <t>75327</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>101684</t>
+          <t>101972</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25461</t>
+          <t>26062</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42738</t>
+          <t>42782</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28588</t>
+          <t>27616</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46343</t>
+          <t>46329</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>59567</t>
+          <t>57392</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84628</t>
+          <t>82897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32975</t>
+          <t>33039</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>51767</t>
+          <t>51631</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,82 +10529,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>30,03%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>44724</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>35315</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>54960</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>20,9%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>32,53%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>86449</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>73097</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>102647</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>25,36%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>21,44%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>30,11%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>44724</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>35698</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>55660</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>26,47%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>86449</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>72531</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>98426</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>25,36%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>21,28%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>20211</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38022</t>
+          <t>37469</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>50388</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>54673</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>81446</t>
+          <t>80574</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>94334</t>
+          <t>94474</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>126790</t>
+          <t>125340</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>86202</t>
+          <t>84412</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>115603</t>
+          <t>114874</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>187369</t>
+          <t>188046</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>233575</t>
+          <t>231128</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>144030</t>
+          <t>143910</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>180718</t>
+          <t>180375</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>153954</t>
+          <t>154622</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>190250</t>
+          <t>192230</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>307403</t>
+          <t>306613</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>359559</t>
+          <t>361253</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>127943</t>
+          <t>128768</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>163555</t>
+          <t>163144</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>138435</t>
+          <t>139191</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>178121</t>
+          <t>175069</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>279093</t>
+          <t>279524</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>328278</t>
+          <t>329100</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>185992</t>
+          <t>187938</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>225191</t>
+          <t>226371</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>204427</t>
+          <t>205997</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>245682</t>
+          <t>245394</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>402280</t>
+          <t>403639</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>459367</t>
+          <t>459626</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
